--- a/data/trans_dic/P7_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P7_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,2; 35,22</t>
+          <t>29,16; 35,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,0; 38,22</t>
+          <t>31,84; 38,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,81; 36,38</t>
+          <t>29,53; 36,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,77; 43,57</t>
+          <t>35,79; 43,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,75; 52,28</t>
+          <t>46,98; 52,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,31; 49,87</t>
+          <t>44,01; 49,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,92; 48,78</t>
+          <t>42,28; 48,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,6; 55,11</t>
+          <t>49,17; 55,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,92; 44,05</t>
+          <t>40,07; 44,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,66; 43,88</t>
+          <t>39,83; 44,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,92; 42,55</t>
+          <t>37,91; 42,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,7; 49,48</t>
+          <t>44,65; 49,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,47</t>
+          <t>6,6; 9,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,58</t>
+          <t>8,74; 11,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 13,62</t>
+          <t>10,63; 13,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 15,12</t>
+          <t>8,98; 15,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,01; 17,58</t>
+          <t>13,73; 17,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 18,15</t>
+          <t>14,36; 18,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,91</t>
+          <t>15,19; 18,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,58; 18,41</t>
+          <t>11,8; 18,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 12,83</t>
+          <t>10,63; 12,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,14</t>
+          <t>11,75; 14,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,41; 15,64</t>
+          <t>13,45; 15,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 16,21</t>
+          <t>11,69; 16,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,28</t>
+          <t>6,07; 11,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,24</t>
+          <t>3,94; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,2</t>
+          <t>3,97; 8,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 13,37</t>
+          <t>8,65; 13,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 17,83</t>
+          <t>11,29; 17,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,47</t>
+          <t>5,39; 10,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 12,75</t>
+          <t>7,43; 12,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,31</t>
+          <t>8,61; 12,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,44</t>
+          <t>9,18; 13,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,03</t>
+          <t>5,14; 8,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,88</t>
+          <t>6,29; 9,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,29</t>
+          <t>9,14; 12,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 16,89</t>
+          <t>14,38; 16,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 17,96</t>
+          <t>15,39; 18,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 17,18</t>
+          <t>14,53; 17,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 18,4</t>
+          <t>12,5; 18,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,94; 30,19</t>
+          <t>27,03; 30,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,28; 28,19</t>
+          <t>25,08; 28,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,45</t>
+          <t>22,5; 25,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 24,26</t>
+          <t>18,06; 24,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,21; 23,28</t>
+          <t>21,29; 23,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 22,77</t>
+          <t>20,78; 22,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,97; 20,91</t>
+          <t>19,03; 20,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 21,08</t>
+          <t>16,95; 20,98</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>301264; 363340</t>
+          <t>300821; 361502</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311889; 372497</t>
+          <t>310355; 372784</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224897; 274469</t>
+          <t>222736; 274816</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184195; 224361</t>
+          <t>184316; 223665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>614768; 687498</t>
+          <t>617854; 690770</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>592295; 666753</t>
+          <t>588374; 662065</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>415228; 483150</t>
+          <t>418787; 483812</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>374745; 416398</t>
+          <t>371506; 415695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>936911; 1033771</t>
+          <t>940363; 1034487</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>916655; 1014262</t>
+          <t>920781; 1016951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>661703; 742428</t>
+          <t>661533; 742320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>567893; 628604</t>
+          <t>567274; 627514</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>113316; 160245</t>
+          <t>111700; 158309</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172034; 226832</t>
+          <t>171197; 229074</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>222406; 282494</t>
+          <t>220530; 283768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>210051; 346316</t>
+          <t>205671; 343694</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>222456; 279042</t>
+          <t>218044; 278440</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>252257; 318524</t>
+          <t>251924; 317285</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>307193; 375917</t>
+          <t>302089; 373663</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>259036; 411920</t>
+          <t>264092; 408344</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>347948; 420837</t>
+          <t>348669; 421434</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>441102; 524975</t>
+          <t>436345; 522659</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>544747; 635326</t>
+          <t>546496; 641424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>514458; 733953</t>
+          <t>529459; 733441</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34510; 62194</t>
+          <t>33488; 61488</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18597; 44304</t>
+          <t>18890; 44413</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21265; 44595</t>
+          <t>21594; 44758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53920; 86456</t>
+          <t>55960; 84869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52490; 84959</t>
+          <t>53801; 84438</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23384; 47921</t>
+          <t>24667; 49916</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41491; 69909</t>
+          <t>40731; 70737</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56334; 81292</t>
+          <t>56885; 81773</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>95181; 138152</t>
+          <t>94395; 136787</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48864; 84578</t>
+          <t>48141; 83217</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68609; 107914</t>
+          <t>68659; 104835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>118476; 160622</t>
+          <t>119413; 159329</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>473016; 553293</t>
+          <t>471042; 554950</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>524893; 612932</t>
+          <t>525102; 615553</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>492772; 579334</t>
+          <t>490087; 576021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>445307; 635052</t>
+          <t>431418; 629045</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>910198; 1020177</t>
+          <t>913456; 1021116</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>897178; 1000745</t>
+          <t>890188; 999385</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>791237; 897628</t>
+          <t>793683; 899135</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>658564; 886429</t>
+          <t>659951; 888723</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1411771; 1549058</t>
+          <t>1417103; 1550198</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1444109; 1585120</t>
+          <t>1446873; 1586909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1308717; 1442626</t>
+          <t>1313138; 1444586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1213474; 1497816</t>
+          <t>1204101; 1491107</t>
         </is>
       </c>
     </row>
